--- a/assessment_forms/014_financial_wellness_assessment--assessment_forms.xlsx
+++ b/assessment_forms/014_financial_wellness_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -949,8 +949,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -978,12 +978,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'under_50k'}</t>
+          <t>under_50k</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Under 50K'}</t>
+          <t>Under 50K</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'50k_to_100k'}</t>
+          <t>50k_to_100k</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '50K to 100K'}</t>
+          <t>50K to 100K</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'100k_to_150k'}</t>
+          <t>100k_to_150k</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '100K to 150K'}</t>
+          <t>100K to 150K</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'150k_to_200k'}</t>
+          <t>150k_to_200k</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '150K to 200K'}</t>
+          <t>150K to 200K</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'200k+'}</t>
+          <t>200k+</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '200K+'}</t>
+          <t>200K+</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'checking'}</t>
+          <t>checking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Checking'}</t>
+          <t>Checking</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'savings'}</t>
+          <t>savings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Savings'}</t>
+          <t>Savings</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'investment'}</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Investment'}</t>
+          <t>Investment</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'retirement'}</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Retirement'}</t>
+          <t>Retirement</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_10k'}</t>
+          <t>less_than_10k</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 10K'}</t>
+          <t>Less than 10K</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'10k_to_20k'}</t>
+          <t>10k_to_20k</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '10K to 20K'}</t>
+          <t>10K to 20K</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'20k+'}</t>
+          <t>20k+</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '20K+'}</t>
+          <t>20K+</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'20%_or_more'}</t>
+          <t>20%_or_more</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': '20% or more'}</t>
+          <t>20% or more</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'40-60%'}</t>
+          <t>40-60%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': '40-60%'}</t>
+          <t>40-60%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'70-80%'}</t>
+          <t>70-80%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': '70-80%'}</t>
+          <t>70-80%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'90%+'}</t>
+          <t>90%+</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': '90%+'}</t>
+          <t>90%+</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'20%_or_more'}</t>
+          <t>20%_or_more</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': '20% or more'}</t>
+          <t>20% or more</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'40-60%'}</t>
+          <t>40-60%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': '40-60%'}</t>
+          <t>40-60%</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'70-80%'}</t>
+          <t>70-80%</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': '70-80%'}</t>
+          <t>70-80%</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'90%+'}</t>
+          <t>90%+</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': '90%+'}</t>
+          <t>90%+</t>
         </is>
       </c>
     </row>
